--- a/Proyecto Interno/mapa/Grupos de alimentos.xlsx
+++ b/Proyecto Interno/mapa/Grupos de alimentos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://javerianacaliedu-my.sharepoint.com/personal/stefens07_javerianacali_edu_co/Documents/CIAT/2. Ejecución/Bases de datos procesadas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/mapa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="11_23A6208D7C699BC31713AB8D178DA9617E50FEFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD189536-B07C-4EAA-8BE3-F03178F1D016}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="11_23A6208D7C699BC31713AB8D178DA9617E50FEFA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E474C043-89AD-4CF9-9825-CF0C9ABD4C14}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -973,6 +973,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -3104,18 +3105,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3138,18 +3139,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2AC6605-6B0E-49FF-A37D-391FFDE8EE44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD9B7A9D-1E27-44D0-B8E8-A3C331602B3F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2AC6605-6B0E-49FF-A37D-391FFDE8EE44}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>